--- a/Statistics/Section 2 - Descriptive Statistics Fundamentals/10_Standard deviation and coefficient of variation/Exercises/2.10.Standard-deviation-and-coefficient-of-variation-exercise-solution.xlsx
+++ b/Statistics/Section 2 - Descriptive Statistics Fundamentals/10_Standard deviation and coefficient of variation/Exercises/2.10.Standard-deviation-and-coefficient-of-variation-exercise-solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iliya Valchanov\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics\Section 2 - Descriptive Statistics Fundamentals\10_Standard deviation and coefficient of variation_\Exercises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F16DCB8F-9E2C-493B-8792-8D9EA9FD9786}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3236B61D-0647-4647-B670-293B420EA40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Std and cv" sheetId="9" r:id="rId1"/>
@@ -21,11 +21,8 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -168,10 +165,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;\²\ * #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ [$kr.-406]"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ [$kr.²-406]"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;\²\ * #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ [$kr.-406]"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00\ [$kr.²-406]"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -248,7 +245,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -258,23 +255,23 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
